--- a/Instruction_Word_Table.xlsx
+++ b/Instruction_Word_Table.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Projects\RISC-V\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Apex\Projects\RISC-V_Project\sfm_RISC-V\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D5834E34-754C-4CCB-B6B9-8F35E20FE57F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E3100FD-49FA-4802-A84A-C6E1EDA8443E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" xr2:uid="{DAA87B19-7E53-4FE8-8CCB-2B72675DA490}"/>
+    <workbookView xWindow="3040" yWindow="2950" windowWidth="28800" windowHeight="15360" xr2:uid="{DAA87B19-7E53-4FE8-8CCB-2B72675DA490}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="2" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="375" uniqueCount="135">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="376" uniqueCount="136">
   <si>
     <t>Instruction</t>
   </si>
@@ -444,6 +444,9 @@
   </si>
   <si>
     <t>Branches (jump conditionals) SCRAMBLED</t>
+  </si>
+  <si>
+    <t>-Need to unscramble</t>
   </si>
 </sst>
 </file>
@@ -515,12 +518,6 @@
     <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -528,7 +525,13 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -866,17 +869,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8FC39E31-91A3-430A-827B-8D1C1B6215BF}">
   <dimension ref="A2:K53"/>
-  <sheetFormatPr defaultRowHeight="14.6"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="18.4609375" customWidth="1"/>
-    <col min="2" max="2" width="18.69140625" customWidth="1"/>
-    <col min="3" max="3" width="18.53515625" customWidth="1"/>
-    <col min="4" max="4" width="18.3828125" customWidth="1"/>
-    <col min="5" max="5" width="18.69140625" customWidth="1"/>
-    <col min="6" max="6" width="18.61328125" customWidth="1"/>
-    <col min="7" max="7" width="18.69140625" customWidth="1"/>
-    <col min="8" max="8" width="18.4609375" customWidth="1"/>
-    <col min="9" max="9" width="37.15234375" customWidth="1"/>
+    <col min="1" max="1" width="18.453125" customWidth="1"/>
+    <col min="2" max="2" width="18.7265625" customWidth="1"/>
+    <col min="3" max="3" width="18.54296875" customWidth="1"/>
+    <col min="4" max="4" width="18.36328125" customWidth="1"/>
+    <col min="5" max="5" width="18.7265625" customWidth="1"/>
+    <col min="6" max="6" width="18.6328125" customWidth="1"/>
+    <col min="7" max="7" width="18.7265625" customWidth="1"/>
+    <col min="8" max="8" width="18.453125" customWidth="1"/>
+    <col min="9" max="9" width="37.1796875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="1:9">
@@ -962,7 +965,7 @@
       <c r="H4" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="I4" s="7" t="s">
+      <c r="I4" s="5" t="s">
         <v>78</v>
       </c>
     </row>
@@ -991,7 +994,7 @@
       <c r="H5" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="I5" s="7" t="s">
+      <c r="I5" s="5" t="s">
         <v>82</v>
       </c>
     </row>
@@ -1020,7 +1023,7 @@
       <c r="H6" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="I6" s="7" t="s">
+      <c r="I6" s="5" t="s">
         <v>85</v>
       </c>
     </row>
@@ -1049,7 +1052,7 @@
       <c r="H7" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="I7" s="7" t="s">
+      <c r="I7" s="5" t="s">
         <v>86</v>
       </c>
     </row>
@@ -1078,7 +1081,7 @@
       <c r="H8" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="I8" s="7" t="s">
+      <c r="I8" s="5" t="s">
         <v>79</v>
       </c>
     </row>
@@ -1107,7 +1110,7 @@
       <c r="H9" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="I9" s="7" t="s">
+      <c r="I9" s="5" t="s">
         <v>83</v>
       </c>
     </row>
@@ -1136,7 +1139,7 @@
       <c r="H10" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="I10" s="7" t="s">
+      <c r="I10" s="5" t="s">
         <v>84</v>
       </c>
     </row>
@@ -1165,7 +1168,7 @@
       <c r="H11" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="I11" s="7" t="s">
+      <c r="I11" s="5" t="s">
         <v>80</v>
       </c>
     </row>
@@ -1194,12 +1197,12 @@
       <c r="H12" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="I12" s="7" t="s">
+      <c r="I12" s="5" t="s">
         <v>81</v>
       </c>
     </row>
     <row r="13" spans="1:9">
-      <c r="I13" s="7"/>
+      <c r="I13" s="5"/>
     </row>
     <row r="14" spans="1:9">
       <c r="A14" s="1" t="s">
@@ -1226,7 +1229,7 @@
       <c r="H14" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="I14" s="7" t="s">
+      <c r="I14" s="5" t="s">
         <v>93</v>
       </c>
     </row>
@@ -1255,7 +1258,7 @@
       <c r="H15" s="3">
         <v>1100111</v>
       </c>
-      <c r="I15" s="7" t="s">
+      <c r="I15" s="5" t="s">
         <v>111</v>
       </c>
     </row>
@@ -1284,7 +1287,7 @@
       <c r="H16" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="I16" s="7" t="s">
+      <c r="I16" s="5" t="s">
         <v>97</v>
       </c>
     </row>
@@ -1313,7 +1316,7 @@
       <c r="H17" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="I17" s="7" t="s">
+      <c r="I17" s="5" t="s">
         <v>98</v>
       </c>
     </row>
@@ -1342,7 +1345,7 @@
       <c r="H18" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="I18" s="7" t="s">
+      <c r="I18" s="5" t="s">
         <v>99</v>
       </c>
     </row>
@@ -1371,7 +1374,7 @@
       <c r="H19" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="I19" s="7" t="s">
+      <c r="I19" s="5" t="s">
         <v>100</v>
       </c>
     </row>
@@ -1400,7 +1403,7 @@
       <c r="H20" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="I20" s="7" t="s">
+      <c r="I20" s="5" t="s">
         <v>101</v>
       </c>
     </row>
@@ -1429,7 +1432,7 @@
       <c r="H21" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="I21" s="7" t="s">
+      <c r="I21" s="5" t="s">
         <v>96</v>
       </c>
     </row>
@@ -1458,7 +1461,7 @@
       <c r="H22" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="I22" s="7" t="s">
+      <c r="I22" s="5" t="s">
         <v>94</v>
       </c>
     </row>
@@ -1487,7 +1490,7 @@
       <c r="H23" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="I23" s="7" t="s">
+      <c r="I23" s="5" t="s">
         <v>95</v>
       </c>
     </row>
@@ -1516,7 +1519,7 @@
       <c r="H24" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="I24" s="7" t="s">
+      <c r="I24" s="5" t="s">
         <v>87</v>
       </c>
     </row>
@@ -1545,7 +1548,7 @@
       <c r="H25" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="I25" s="7" t="s">
+      <c r="I25" s="5" t="s">
         <v>89</v>
       </c>
     </row>
@@ -1574,11 +1577,11 @@
       <c r="H26" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="I26" s="7" t="s">
+      <c r="I26" s="5" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="27" spans="1:9" ht="28.3" customHeight="1">
+    <row r="27" spans="1:9" ht="28.25" customHeight="1">
       <c r="A27" s="1" t="s">
         <v>39</v>
       </c>
@@ -1603,11 +1606,11 @@
       <c r="H27" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="I27" s="7" t="s">
+      <c r="I27" s="5" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="28" spans="1:9" ht="28.3" customHeight="1">
+    <row r="28" spans="1:9" ht="28.25" customHeight="1">
       <c r="A28" s="1" t="s">
         <v>40</v>
       </c>
@@ -1632,11 +1635,11 @@
       <c r="H28" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="I28" s="7" t="s">
+      <c r="I28" s="5" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="29" spans="1:9" ht="28.3" customHeight="1">
+    <row r="29" spans="1:9" ht="28.25" customHeight="1">
       <c r="A29" s="1" t="s">
         <v>41</v>
       </c>
@@ -1661,7 +1664,7 @@
       <c r="H29" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="I29" s="7" t="s">
+      <c r="I29" s="5" t="s">
         <v>92</v>
       </c>
     </row>
@@ -1690,7 +1693,7 @@
       <c r="H30" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="I30" s="7" t="s">
+      <c r="I30" s="5" t="s">
         <v>112</v>
       </c>
     </row>
@@ -1719,7 +1722,7 @@
       <c r="H31" s="3">
         <v>1110011</v>
       </c>
-      <c r="I31" s="7" t="s">
+      <c r="I31" s="5" t="s">
         <v>112</v>
       </c>
     </row>
@@ -1748,20 +1751,20 @@
       <c r="H32" s="3">
         <v>1110011</v>
       </c>
-      <c r="I32" s="7" t="s">
+      <c r="I32" s="5" t="s">
         <v>112</v>
       </c>
     </row>
     <row r="33" spans="1:11">
-      <c r="A33" s="6"/>
-      <c r="B33" s="6"/>
-      <c r="C33" s="6"/>
-      <c r="D33" s="6"/>
-      <c r="E33" s="6"/>
-      <c r="F33" s="6"/>
-      <c r="G33" s="6"/>
-      <c r="H33" s="6"/>
-      <c r="I33" s="7"/>
+      <c r="A33" s="4"/>
+      <c r="B33" s="4"/>
+      <c r="C33" s="4"/>
+      <c r="D33" s="4"/>
+      <c r="E33" s="4"/>
+      <c r="F33" s="4"/>
+      <c r="G33" s="4"/>
+      <c r="H33" s="4"/>
+      <c r="I33" s="5"/>
     </row>
     <row r="34" spans="1:11">
       <c r="A34" s="1" t="s">
@@ -1788,7 +1791,7 @@
       <c r="H34" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="I34" s="7" t="s">
+      <c r="I34" s="5" t="s">
         <v>114</v>
       </c>
     </row>
@@ -1817,7 +1820,7 @@
       <c r="H35" s="3">
         <v>100011</v>
       </c>
-      <c r="I35" s="7" t="s">
+      <c r="I35" s="5" t="s">
         <v>116</v>
       </c>
     </row>
@@ -1846,7 +1849,7 @@
       <c r="H36" s="3">
         <v>100011</v>
       </c>
-      <c r="I36" s="7" t="s">
+      <c r="I36" s="5" t="s">
         <v>115</v>
       </c>
     </row>
@@ -1875,12 +1878,12 @@
       <c r="H37" s="3">
         <v>100011</v>
       </c>
-      <c r="I37" s="7" t="s">
+      <c r="I37" s="5" t="s">
         <v>117</v>
       </c>
     </row>
     <row r="38" spans="1:11">
-      <c r="I38" s="7"/>
+      <c r="I38" s="5"/>
     </row>
     <row r="39" spans="1:11">
       <c r="A39" s="1" t="s">
@@ -1907,8 +1910,11 @@
       <c r="H39" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="I39" s="7" t="s">
+      <c r="I39" s="5" t="s">
         <v>134</v>
+      </c>
+      <c r="J39" s="4" t="s">
+        <v>135</v>
       </c>
     </row>
     <row r="40" spans="1:11">
@@ -1936,7 +1942,7 @@
       <c r="H40" s="3">
         <v>1100011</v>
       </c>
-      <c r="I40" s="7" t="s">
+      <c r="I40" s="5" t="s">
         <v>120</v>
       </c>
     </row>
@@ -1965,7 +1971,7 @@
       <c r="H41" s="3">
         <v>1100011</v>
       </c>
-      <c r="I41" s="7" t="s">
+      <c r="I41" s="5" t="s">
         <v>121</v>
       </c>
     </row>
@@ -1994,7 +2000,7 @@
       <c r="H42" s="3">
         <v>1100011</v>
       </c>
-      <c r="I42" s="7" t="s">
+      <c r="I42" s="5" t="s">
         <v>122</v>
       </c>
     </row>
@@ -2023,7 +2029,7 @@
       <c r="H43" s="3">
         <v>1100011</v>
       </c>
-      <c r="I43" s="7" t="s">
+      <c r="I43" s="5" t="s">
         <v>123</v>
       </c>
     </row>
@@ -2052,7 +2058,7 @@
       <c r="H44" s="3">
         <v>1100011</v>
       </c>
-      <c r="I44" s="7" t="s">
+      <c r="I44" s="5" t="s">
         <v>124</v>
       </c>
     </row>
@@ -2081,7 +2087,7 @@
       <c r="H45" s="3">
         <v>1100011</v>
       </c>
-      <c r="I45" s="7" t="s">
+      <c r="I45" s="5" t="s">
         <v>125</v>
       </c>
     </row>
@@ -2094,7 +2100,7 @@
       <c r="F46" s="2"/>
       <c r="G46" s="2"/>
       <c r="H46" s="2"/>
-      <c r="I46" s="7"/>
+      <c r="I46" s="5"/>
     </row>
     <row r="47" spans="1:11">
       <c r="A47" s="1" t="s">
@@ -2103,19 +2109,19 @@
       <c r="B47" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C47" s="4" t="s">
+      <c r="C47" s="9" t="s">
         <v>110</v>
       </c>
-      <c r="D47" s="4"/>
-      <c r="E47" s="4"/>
-      <c r="F47" s="4"/>
+      <c r="D47" s="9"/>
+      <c r="E47" s="9"/>
+      <c r="F47" s="9"/>
       <c r="G47" s="1" t="s">
         <v>2</v>
       </c>
       <c r="H47" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="I47" s="9"/>
+      <c r="I47" s="7"/>
       <c r="J47" s="2"/>
       <c r="K47" s="2"/>
     </row>
@@ -2126,19 +2132,19 @@
       <c r="B48" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C48" s="5" t="s">
+      <c r="C48" s="8" t="s">
         <v>68</v>
       </c>
-      <c r="D48" s="5"/>
-      <c r="E48" s="5"/>
-      <c r="F48" s="5"/>
+      <c r="D48" s="8"/>
+      <c r="E48" s="8"/>
+      <c r="F48" s="8"/>
       <c r="G48" s="2" t="s">
         <v>7</v>
       </c>
       <c r="H48" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="I48" s="9" t="s">
+      <c r="I48" s="7" t="s">
         <v>126</v>
       </c>
       <c r="J48" s="2"/>
@@ -2151,24 +2157,24 @@
       <c r="B49" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C49" s="5" t="s">
+      <c r="C49" s="8" t="s">
         <v>68</v>
       </c>
-      <c r="D49" s="5"/>
-      <c r="E49" s="5"/>
-      <c r="F49" s="5"/>
+      <c r="D49" s="8"/>
+      <c r="E49" s="8"/>
+      <c r="F49" s="8"/>
       <c r="G49" s="2" t="s">
         <v>7</v>
       </c>
       <c r="H49" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="I49" s="7" t="s">
+      <c r="I49" s="5" t="s">
         <v>127</v>
       </c>
     </row>
     <row r="50" spans="1:9">
-      <c r="I50" s="7"/>
+      <c r="I50" s="5"/>
     </row>
     <row r="51" spans="1:9">
       <c r="A51" s="1" t="s">
@@ -2195,7 +2201,7 @@
       <c r="H51" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="I51" s="7" t="s">
+      <c r="I51" s="5" t="s">
         <v>133</v>
       </c>
     </row>
@@ -2224,12 +2230,12 @@
       <c r="H52" s="3">
         <v>1101111</v>
       </c>
-      <c r="I52" s="7" t="s">
+      <c r="I52" s="5" t="s">
         <v>132</v>
       </c>
     </row>
     <row r="53" spans="1:9">
-      <c r="I53" s="8"/>
+      <c r="I53" s="6"/>
     </row>
   </sheetData>
   <mergeCells count="3">

--- a/Instruction_Word_Table.xlsx
+++ b/Instruction_Word_Table.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Apex\Projects\RISC-V_Project\sfm_RISC-V\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E3100FD-49FA-4802-A84A-C6E1EDA8443E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30D5BA50-D8F5-4BFF-89F4-7AC9B9202577}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3040" yWindow="2950" windowWidth="28800" windowHeight="15360" xr2:uid="{DAA87B19-7E53-4FE8-8CCB-2B72675DA490}"/>
+    <workbookView xWindow="45972" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{DAA87B19-7E53-4FE8-8CCB-2B72675DA490}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="2" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="376" uniqueCount="136">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="377" uniqueCount="137">
   <si>
     <t>Instruction</t>
   </si>
@@ -269,9 +269,6 @@
     <t>00001</t>
   </si>
   <si>
-    <t>Func7/Immediate0</t>
-  </si>
-  <si>
     <t>rs1 + rs2 = rd</t>
   </si>
   <si>
@@ -446,7 +443,13 @@
     <t>Branches (jump conditionals) SCRAMBLED</t>
   </si>
   <si>
-    <t>-Need to unscramble</t>
+    <t>imm[12] imm[10:5] rs2 rs1 funct3 imm[4:1] imm[11] opcode</t>
+  </si>
+  <si>
+    <t>imm[20] imm[10:1] imm[11] imm[19:12] rd opcode</t>
+  </si>
+  <si>
+    <t>Func7/Imm0</t>
   </si>
 </sst>
 </file>
@@ -507,7 +510,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -533,6 +536,9 @@
     </xf>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -868,7 +874,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8FC39E31-91A3-430A-827B-8D1C1B6215BF}">
-  <dimension ref="A2:K53"/>
+  <dimension ref="A2:K54"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="18.453125" customWidth="1"/>
@@ -890,16 +896,16 @@
         <v>1</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>2</v>
@@ -937,7 +943,7 @@
         <v>67</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="4" spans="1:9">
@@ -966,7 +972,7 @@
         <v>67</v>
       </c>
       <c r="I4" s="5" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="5" spans="1:9">
@@ -995,7 +1001,7 @@
         <v>67</v>
       </c>
       <c r="I5" s="5" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="6" spans="1:9">
@@ -1024,7 +1030,7 @@
         <v>67</v>
       </c>
       <c r="I6" s="5" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="7" spans="1:9">
@@ -1053,7 +1059,7 @@
         <v>67</v>
       </c>
       <c r="I7" s="5" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="8" spans="1:9">
@@ -1082,7 +1088,7 @@
         <v>67</v>
       </c>
       <c r="I8" s="5" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="9" spans="1:9">
@@ -1111,7 +1117,7 @@
         <v>67</v>
       </c>
       <c r="I9" s="5" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="10" spans="1:9">
@@ -1140,7 +1146,7 @@
         <v>67</v>
       </c>
       <c r="I10" s="5" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -1169,7 +1175,7 @@
         <v>67</v>
       </c>
       <c r="I11" s="5" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="12" spans="1:9">
@@ -1198,7 +1204,7 @@
         <v>67</v>
       </c>
       <c r="I12" s="5" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="13" spans="1:9">
@@ -1212,16 +1218,16 @@
         <v>1</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>76</v>
+        <v>136</v>
       </c>
       <c r="D14" s="1" t="s">
         <v>71</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="G14" s="1" t="s">
         <v>2</v>
@@ -1230,7 +1236,7 @@
         <v>3</v>
       </c>
       <c r="I14" s="5" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="15" spans="1:9">
@@ -1259,7 +1265,7 @@
         <v>1100111</v>
       </c>
       <c r="I15" s="5" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="16" spans="1:9">
@@ -1288,7 +1294,7 @@
         <v>63</v>
       </c>
       <c r="I16" s="5" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="17" spans="1:9">
@@ -1317,7 +1323,7 @@
         <v>63</v>
       </c>
       <c r="I17" s="5" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="18" spans="1:9">
@@ -1346,7 +1352,7 @@
         <v>63</v>
       </c>
       <c r="I18" s="5" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="19" spans="1:9">
@@ -1375,7 +1381,7 @@
         <v>63</v>
       </c>
       <c r="I19" s="5" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="20" spans="1:9">
@@ -1404,7 +1410,7 @@
         <v>63</v>
       </c>
       <c r="I20" s="5" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="21" spans="1:9">
@@ -1433,7 +1439,7 @@
         <v>64</v>
       </c>
       <c r="I21" s="5" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="22" spans="1:9">
@@ -1462,7 +1468,7 @@
         <v>64</v>
       </c>
       <c r="I22" s="5" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="23" spans="1:9">
@@ -1491,7 +1497,7 @@
         <v>64</v>
       </c>
       <c r="I23" s="5" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="24" spans="1:9">
@@ -1520,7 +1526,7 @@
         <v>64</v>
       </c>
       <c r="I24" s="5" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="25" spans="1:9">
@@ -1549,7 +1555,7 @@
         <v>64</v>
       </c>
       <c r="I25" s="5" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="26" spans="1:9">
@@ -1578,7 +1584,7 @@
         <v>64</v>
       </c>
       <c r="I26" s="5" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="27" spans="1:9" ht="28.25" customHeight="1">
@@ -1607,7 +1613,7 @@
         <v>64</v>
       </c>
       <c r="I27" s="5" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="28" spans="1:9" ht="28.25" customHeight="1">
@@ -1636,7 +1642,7 @@
         <v>64</v>
       </c>
       <c r="I28" s="5" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="29" spans="1:9" ht="28.25" customHeight="1">
@@ -1665,7 +1671,7 @@
         <v>64</v>
       </c>
       <c r="I29" s="5" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="30" spans="1:9">
@@ -1694,7 +1700,7 @@
         <v>65</v>
       </c>
       <c r="I30" s="5" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="31" spans="1:9">
@@ -1723,7 +1729,7 @@
         <v>1110011</v>
       </c>
       <c r="I31" s="5" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="32" spans="1:9">
@@ -1752,7 +1758,7 @@
         <v>1110011</v>
       </c>
       <c r="I32" s="5" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="33" spans="1:11">
@@ -1774,25 +1780,25 @@
         <v>1</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="G34" s="1" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="H34" s="1" t="s">
         <v>3</v>
       </c>
       <c r="I34" s="5" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="35" spans="1:11">
@@ -1815,13 +1821,13 @@
         <v>58</v>
       </c>
       <c r="G35" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="H35" s="3">
         <v>100011</v>
       </c>
       <c r="I35" s="5" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="36" spans="1:11">
@@ -1844,13 +1850,13 @@
         <v>59</v>
       </c>
       <c r="G36" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="H36" s="3">
         <v>100011</v>
       </c>
       <c r="I36" s="5" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="37" spans="1:11">
@@ -1873,13 +1879,13 @@
         <v>60</v>
       </c>
       <c r="G37" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="H37" s="3">
         <v>100011</v>
       </c>
       <c r="I37" s="5" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="38" spans="1:11">
@@ -1893,16 +1899,16 @@
         <v>1</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D39" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="E39" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="E39" s="1" t="s">
-        <v>105</v>
-      </c>
       <c r="F39" s="1" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="G39" s="1" t="s">
         <v>66</v>
@@ -1911,11 +1917,9 @@
         <v>3</v>
       </c>
       <c r="I39" s="5" t="s">
-        <v>134</v>
-      </c>
-      <c r="J39" s="4" t="s">
-        <v>135</v>
-      </c>
+        <v>133</v>
+      </c>
+      <c r="J39" s="4"/>
     </row>
     <row r="40" spans="1:11">
       <c r="A40" s="1" t="s">
@@ -1943,7 +1947,7 @@
         <v>1100011</v>
       </c>
       <c r="I40" s="5" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="41" spans="1:11">
@@ -1972,7 +1976,7 @@
         <v>1100011</v>
       </c>
       <c r="I41" s="5" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="42" spans="1:11">
@@ -2001,7 +2005,7 @@
         <v>1100011</v>
       </c>
       <c r="I42" s="5" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="43" spans="1:11">
@@ -2030,7 +2034,7 @@
         <v>1100011</v>
       </c>
       <c r="I43" s="5" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="44" spans="1:11">
@@ -2059,7 +2063,7 @@
         <v>1100011</v>
       </c>
       <c r="I44" s="5" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="45" spans="1:11">
@@ -2088,71 +2092,59 @@
         <v>1100011</v>
       </c>
       <c r="I45" s="5" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="46" spans="1:11">
-      <c r="A46" s="1"/>
-      <c r="B46" s="2"/>
-      <c r="C46" s="2"/>
-      <c r="D46" s="2"/>
-      <c r="E46" s="2"/>
-      <c r="F46" s="2"/>
-      <c r="G46" s="2"/>
-      <c r="H46" s="2"/>
+      <c r="A46" s="8" t="s">
+        <v>134</v>
+      </c>
+      <c r="B46" s="9"/>
+      <c r="C46" s="9"/>
+      <c r="D46" s="9"/>
+      <c r="E46" s="9"/>
+      <c r="F46" s="9"/>
+      <c r="G46" s="9"/>
+      <c r="H46" s="9"/>
       <c r="I46" s="5"/>
     </row>
     <row r="47" spans="1:11">
-      <c r="A47" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B47" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C47" s="9" t="s">
-        <v>110</v>
-      </c>
-      <c r="D47" s="9"/>
-      <c r="E47" s="9"/>
-      <c r="F47" s="9"/>
-      <c r="G47" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="H47" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="I47" s="7"/>
-      <c r="J47" s="2"/>
-      <c r="K47" s="2"/>
+      <c r="A47" s="1"/>
+      <c r="B47" s="2"/>
+      <c r="C47" s="2"/>
+      <c r="D47" s="2"/>
+      <c r="E47" s="2"/>
+      <c r="F47" s="2"/>
+      <c r="G47" s="2"/>
+      <c r="H47" s="2"/>
+      <c r="I47" s="5"/>
     </row>
     <row r="48" spans="1:11">
       <c r="A48" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B48" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C48" s="8" t="s">
-        <v>68</v>
-      </c>
-      <c r="D48" s="8"/>
-      <c r="E48" s="8"/>
-      <c r="F48" s="8"/>
-      <c r="G48" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="H48" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="I48" s="7" t="s">
-        <v>126</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="B48" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C48" s="9" t="s">
+        <v>109</v>
+      </c>
+      <c r="D48" s="9"/>
+      <c r="E48" s="9"/>
+      <c r="F48" s="9"/>
+      <c r="G48" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="H48" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="I48" s="7"/>
       <c r="J48" s="2"/>
       <c r="K48" s="2"/>
     </row>
-    <row r="49" spans="1:9">
+    <row r="49" spans="1:11">
       <c r="A49" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="B49" s="2" t="s">
         <v>6</v>
@@ -2167,81 +2159,118 @@
         <v>7</v>
       </c>
       <c r="H49" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="I49" s="7" t="s">
+        <v>125</v>
+      </c>
+      <c r="J49" s="2"/>
+      <c r="K49" s="2"/>
+    </row>
+    <row r="50" spans="1:11">
+      <c r="A50" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B50" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C50" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="D50" s="8"/>
+      <c r="E50" s="8"/>
+      <c r="F50" s="8"/>
+      <c r="G50" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="H50" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="I49" s="5" t="s">
+      <c r="I50" s="5" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="51" spans="1:11">
+      <c r="I51" s="5"/>
+    </row>
+    <row r="52" spans="1:11">
+      <c r="A52" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B52" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C52" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="D52" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="E52" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="F52" s="1" t="s">
         <v>127</v>
       </c>
-    </row>
-    <row r="50" spans="1:9">
-      <c r="I50" s="5"/>
-    </row>
-    <row r="51" spans="1:9">
-      <c r="A51" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B51" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C51" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="D51" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="E51" s="1" t="s">
-        <v>129</v>
-      </c>
-      <c r="F51" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="G51" s="1" t="s">
+      <c r="G52" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="H51" s="1" t="s">
+      <c r="H52" s="1" t="s">
         <v>3</v>
-      </c>
-      <c r="I51" s="5" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="52" spans="1:9">
-      <c r="A52" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B52" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C52" s="2" t="s">
-        <v>131</v>
-      </c>
-      <c r="D52" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="E52" s="2" t="s">
-        <v>129</v>
-      </c>
-      <c r="F52" s="2" t="s">
-        <v>128</v>
-      </c>
-      <c r="G52" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="H52" s="3">
-        <v>1101111</v>
       </c>
       <c r="I52" s="5" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="53" spans="1:9">
-      <c r="I53" s="6"/>
+    <row r="53" spans="1:11">
+      <c r="A53" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B53" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C53" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="D53" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="E53" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="F53" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="G53" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="H53" s="3">
+        <v>1101111</v>
+      </c>
+      <c r="I53" s="5" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="54" spans="1:11">
+      <c r="A54" s="10" t="s">
+        <v>135</v>
+      </c>
+      <c r="B54" s="10"/>
+      <c r="C54" s="10"/>
+      <c r="D54" s="10"/>
+      <c r="E54" s="10"/>
+      <c r="F54" s="10"/>
+      <c r="G54" s="10"/>
+      <c r="H54" s="10"/>
+      <c r="I54" s="6"/>
     </row>
   </sheetData>
-  <mergeCells count="3">
+  <mergeCells count="5">
+    <mergeCell ref="C50:F50"/>
+    <mergeCell ref="C48:F48"/>
     <mergeCell ref="C49:F49"/>
-    <mergeCell ref="C47:F47"/>
-    <mergeCell ref="C48:F48"/>
+    <mergeCell ref="A46:H46"/>
+    <mergeCell ref="A54:H54"/>
   </mergeCells>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Instruction_Word_Table.xlsx
+++ b/Instruction_Word_Table.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Apex\Projects\RISC-V_Project\sfm_RISC-V\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30D5BA50-D8F5-4BFF-89F4-7AC9B9202577}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6BC5CEA-46F7-4869-B925-952022FB4104}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="45972" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{DAA87B19-7E53-4FE8-8CCB-2B72675DA490}"/>
+    <workbookView xWindow="-38520" yWindow="-120" windowWidth="38640" windowHeight="23520" xr2:uid="{DAA87B19-7E53-4FE8-8CCB-2B72675DA490}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="2" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="377" uniqueCount="137">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="380" uniqueCount="138">
   <si>
     <t>Instruction</t>
   </si>
@@ -450,6 +450,9 @@
   </si>
   <si>
     <t>Func7/Imm0</t>
+  </si>
+  <si>
+    <t>0100011</t>
   </si>
 </sst>
 </file>
@@ -1823,8 +1826,8 @@
       <c r="G35" s="2" t="s">
         <v>118</v>
       </c>
-      <c r="H35" s="3">
-        <v>100011</v>
+      <c r="H35" s="3" t="s">
+        <v>137</v>
       </c>
       <c r="I35" s="5" t="s">
         <v>115</v>
@@ -1852,8 +1855,8 @@
       <c r="G36" s="2" t="s">
         <v>118</v>
       </c>
-      <c r="H36" s="3">
-        <v>100011</v>
+      <c r="H36" s="3" t="s">
+        <v>137</v>
       </c>
       <c r="I36" s="5" t="s">
         <v>114</v>
@@ -1881,8 +1884,8 @@
       <c r="G37" s="2" t="s">
         <v>118</v>
       </c>
-      <c r="H37" s="3">
-        <v>100011</v>
+      <c r="H37" s="3" t="s">
+        <v>137</v>
       </c>
       <c r="I37" s="5" t="s">
         <v>116</v>
